--- a/output/full_scan/batch_seq0_2026-10-13.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-13.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.97669329993366</v>
+        <v>68.97669337957063</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.16788186283525</v>
+        <v>28.16788181641208</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.620366744059519</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2554926100324348</v>
+        <v>0.2554926098521772</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.95856868081884</v>
+        <v>55.95856854814298</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10.45800985475358</v>
+        <v>10.45800986912858</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.253571440041021</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4523643814467675</v>
+        <v>0.4523643828888266</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>56.88114796039607</v>
+        <v>56.88114785399437</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.96075295440414</v>
+        <v>29.96075308506354</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3.225275691170589</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4699474043939133</v>
+        <v>-0.4699474037449804</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>900.7396886871884</v>
+        <v>900.7396886871876</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>101.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>71.5377506065965</v>
+        <v>71.53775120255716</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10.68311465081384</v>
+        <v>10.68311466675066</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6.052710112467934</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.507049437108271</v>
+        <v>1.5070494356662</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>886.8630776050047</v>
+        <v>886.8630776050104</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>52.2</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.96390649259295</v>
+        <v>59.96390663540835</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.19742103127954</v>
+        <v>19.19742105653221</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.941385574661436</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2016593625833006</v>
+        <v>0.2016593623549748</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>90.51149137016654</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28.50744423676912</v>
+        <v>28.50744423345129</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>10.75593351695075</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.14055428104221</v>
+        <v>74.14055437733433</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.56425460147857</v>
+        <v>36.56425473374812</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.73658258151109</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.6093654758893763</v>
+        <v>0.6093654757451683</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.18038554359251</v>
+        <v>65.18038556990646</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.5394201587053</v>
+        <v>35.53942019968341</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.288409462729521</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.368820135580964</v>
+        <v>1.368820135472808</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.17824365532431</v>
+        <v>60.17824378182667</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.5936424881477</v>
+        <v>15.59364236309964</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.05289638309687</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.410646625803684</v>
+        <v>1.410646625202825</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>803.0284020313238</v>
+        <v>803.0284020313229</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1715</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>67.14414721236049</v>
+        <v>67.14414723639973</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>41.78770121718584</v>
+        <v>41.78770118517078</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>2.087208667126042</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11.76516144169645</v>
+        <v>11.76516144001398</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.37959375513051</v>
+        <v>64.37959384741791</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.08994189741466</v>
+        <v>30.08994199466915</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.950267938382388</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4.067857475911607</v>
+        <v>4.067857474950223</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>54.05749985521808</v>
+        <v>54.05749998630913</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.72713114558856</v>
+        <v>36.72713126421239</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.2705633625352961</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.1407884078896986</v>
+        <v>-0.1407884079377657</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.89196429307799</v>
+        <v>56.891964218541</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4.394671318588321</v>
+        <v>4.394671337841542</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.64968019606671</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.24987879320813</v>
+        <v>64.24987902778361</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33.09170377150932</v>
+        <v>33.09170378466663</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.949602267020772</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2416110038238261</v>
+        <v>0.2416110036796168</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>71.42592501222836</v>
+        <v>71.42592505400209</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.18053206552277</v>
+        <v>34.18053202306892</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>3.568436481053747</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.506227752138326</v>
+        <v>3.506227751717721</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>727.8447608558859</v>
+        <v>727.8447608558861</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>8.75</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.29417401334197</v>
+        <v>54.29417405181787</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.46785493125783</v>
+        <v>23.46785503744471</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.34150989905275</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0461697915027509</v>
+        <v>0.0461697914811199</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>64.08191799460113</v>
+        <v>64.08191845925202</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.15129090382123</v>
+        <v>33.15129099345584</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.414649026292067</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1131305194036836</v>
+        <v>0.1131305190191271</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>722.0349855495723</v>
+        <v>722.034985549572</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>21.75</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.33160788210118</v>
+        <v>66.33160822344882</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.04839295026701</v>
+        <v>26.0483928582936</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>2.353600953918693</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1480751172878172</v>
+        <v>0.1480751171676443</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>713.3318538157592</v>
+        <v>713.3318538157581</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>23.8</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>52.09272624770129</v>
+        <v>52.09272626804034</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.820038915252775</v>
+        <v>9.820038900874763</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>4.657573210938005</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3206740155770216</v>
+        <v>0.3206740153967649</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.39391362741314</v>
+        <v>56.39391361999978</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>13.69654423560094</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.40182106492777</v>
+        <v>57.40182106847505</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>41.47789734996044</v>
+        <v>41.47789739094979</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.5757626168798217</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.9359033750265652</v>
+        <v>0.9359033750145364</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.6342009252734</v>
+        <v>65.63420095624947</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.46639682009854</v>
+        <v>29.46639696277004</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.6881234309262346</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>18.99331500822052</v>
+        <v>18.99331500509598</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.3056243148478</v>
+        <v>53.30562439961067</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.87446657664439</v>
+        <v>18.87446676474709</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6288245151971238</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2713330378935728</v>
+        <v>0.271333037617179</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>47.00648625217843</v>
+        <v>47.00648642732506</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.89429538452736</v>
+        <v>23.89429545945162</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.203502378164616</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.32896577318933</v>
+        <v>1.328965771747278</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>646.4516201623071</v>
+        <v>646.4516201623072</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>21</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.04833309227775</v>
+        <v>61.04833298208845</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.71050866190942</v>
+        <v>24.71050882750235</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.314172240475002</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1899519789401249</v>
+        <v>0.1899519790362669</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>642.7559831821196</v>
+        <v>642.7559831821194</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>48.45</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.13265858474489</v>
+        <v>67.13265878553038</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.03197082650975</v>
+        <v>16.031970848427</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.800640555053026</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3256990441512739</v>
+        <v>0.3256990439830265</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.46363489398218</v>
+        <v>51.46363495827789</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>37.84262261679966</v>
+        <v>37.84262287857634</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.4303246570906794</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0890287238988705</v>
+        <v>-0.08902872457183079</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.72040351369515</v>
+        <v>41.72040350002075</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.97349974151562</v>
+        <v>29.97349985244096</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6492955859700905</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-2.417166589655038</v>
+        <v>-2.41716658981981</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8085</v>
+        <v>8201</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>579.5926933678243</v>
+        <v>604.8100550533853</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>14.45</v>
+        <v>15.6</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.38329330137423</v>
+        <v>58.59592053695532</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.6884940151471</v>
+        <v>52.69605181121823</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8726687255748599</v>
+        <v>0.7699647921468585</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0467704648743855</v>
+        <v>0.1666450929647482</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8038</v>
+        <v>8085</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>578.7722383801823</v>
+        <v>579.5926933678243</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>34.85</v>
+        <v>14.45</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.23758916012646</v>
+        <v>50.38329340634827</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.67325864108322</v>
+        <v>20.68849402195185</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5624303340948708</v>
+        <v>0.8726687255748599</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2765087701275543</v>
+        <v>-0.0467704649825415</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8234</v>
+        <v>8038</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>574.852312563859</v>
+        <v>578.7722383801824</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>63.3</v>
+        <v>34.85</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.68380972420506</v>
+        <v>57.23758947745083</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.83195840358668</v>
+        <v>33.67325880550381</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.068355844774635</v>
+        <v>0.5624303340948708</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3384820378606724</v>
+        <v>0.2765087695507214</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8240</v>
+        <v>8234</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>573.3761749591612</v>
+        <v>574.8523125638586</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>51.9</v>
+        <v>63.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.63818361278101</v>
+        <v>48.68381013366248</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.04566733530039</v>
+        <v>16.83195851397208</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4449607364830995</v>
+        <v>1.068355844774635</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.5112013462046523</v>
+        <v>0.3384820365387639</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8112</v>
+        <v>8240</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>572.9377444467085</v>
+        <v>573.3761749591612</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>84.2</v>
+        <v>51.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.19570271669902</v>
+        <v>47.63818369012586</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.02820808560667</v>
+        <v>34.04566739867829</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.119648003272976</v>
+        <v>0.4449607364830995</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.433274000915562</v>
+        <v>-0.511201346481053</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8131</v>
+        <v>8112</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>566.9791683010717</v>
+        <v>572.9377444467085</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.75950356195465</v>
+        <v>45.19570284101808</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.76601175008561</v>
+        <v>17.0282081480669</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.224269130351259</v>
+        <v>1.119648003272976</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.6685512067455297</v>
+        <v>0.433274000687232</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8277</v>
+        <v>8131</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>566.9216633989489</v>
+        <v>566.9791683010828</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15.15</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>74.11595919235037</v>
+        <v>55.75950360420103</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.71100671828757</v>
+        <v>18.76601184044083</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2413604331669732</v>
+        <v>1.224269130351259</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0379070650436283</v>
+        <v>0.6685512066734295</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8926</v>
+        <v>8277</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>559.8431223660344</v>
+        <v>566.9216633989489</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>58.2</v>
+        <v>15.15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.96798576002838</v>
+        <v>74.11595932429005</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.70223753977885</v>
+        <v>37.71100682137842</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.459191012276709</v>
+        <v>0.2413604331669732</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0957229509786435</v>
+        <v>-0.037907065014795</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8440</v>
+        <v>8926</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>556.0495837284182</v>
+        <v>559.8431223660344</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>20.15</v>
+        <v>58.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>49.62998436680947</v>
+        <v>45.96798586165239</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.28686766264205</v>
+        <v>14.70223765381752</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.177783751664931</v>
+        <v>1.459191012276709</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.008254336253643999</v>
+        <v>0.0957229507623394</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8423</v>
+        <v>8440</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>546.4762507567727</v>
+        <v>556.0495837284174</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>17.85</v>
+        <v>20.15</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46.78788155908508</v>
+        <v>49.62998457118543</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.22446522193873</v>
+        <v>20.28686771959334</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2997291278506713</v>
+        <v>1.177783751664931</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0225462955906685</v>
+        <v>-0.008254336325745499</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8043</v>
+        <v>8423</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>541.4677849758444</v>
+        <v>546.4762507567727</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>137</v>
+        <v>17.85</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.43000071058357</v>
+        <v>46.78788165295988</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.16578360881243</v>
+        <v>22.22446527820064</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9412279209893341</v>
+        <v>0.2997291278506713</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.115208808174047</v>
+        <v>-0.022546295602686</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8932</v>
+        <v>8043</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>533.477683445381</v>
+        <v>541.4677849758444</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.0519011344897</v>
+        <v>48.43000073924232</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.54515576116573</v>
+        <v>16.16578373389967</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.433769128419421</v>
+        <v>0.9412279209893341</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.8364726449665854</v>
+        <v>1.115208807897635</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9110</v>
+        <v>8932</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>530.2584512798533</v>
+        <v>533.477683445381</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3.02</v>
+        <v>95</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.74806506588877</v>
+        <v>52.05190169735122</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5.405886582290239</v>
+        <v>17.54515579611628</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6258451279853287</v>
+        <v>1.433769128419421</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0449112898065214</v>
+        <v>0.8364726457904008</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8040</v>
+        <v>9110</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>529.6591205007751</v>
+        <v>530.2584512798533</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>84.3</v>
+        <v>3.02</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.83842616526466</v>
+        <v>51.74806505939342</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.82229253610389</v>
+        <v>5.405886371310478</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2986571146740652</v>
+        <v>0.6258451279853287</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.065376468139823</v>
+        <v>0.0449112898185388</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8438</v>
+        <v>8040</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>524.5358199073713</v>
+        <v>529.6591205007751</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>77.8</v>
+        <v>84.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.30217954055166</v>
+        <v>46.83842620480628</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>31.12443783699005</v>
+        <v>24.82229251222114</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4210247872384492</v>
+        <v>0.2986571146740652</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.079040072190339</v>
+        <v>-1.065376468308067</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8114</v>
+        <v>8438</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>515.7293086851392</v>
+        <v>524.5358199073713</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>180.5</v>
+        <v>77.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.96614923422477</v>
+        <v>55.30217961167244</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.2730912660425</v>
+        <v>31.12443809526616</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8956534518805592</v>
+        <v>0.4210247872384492</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.228142056697923</v>
+        <v>0.0790400720701591</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8249</v>
+        <v>8114</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>514.9230913138938</v>
+        <v>515.7293086851392</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>40.05</v>
+        <v>180.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.25175456045966</v>
+        <v>45.96614911134173</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.70321991723213</v>
+        <v>21.27309127017608</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.657907471799552</v>
+        <v>0.8956534518805592</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.194077912724019</v>
+        <v>1.228142055856702</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8092</v>
+        <v>8249</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>506.2331153808421</v>
+        <v>514.9230913138938</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12.7</v>
+        <v>40.05</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.33847843762705</v>
+        <v>51.25175515053427</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.39221284958288</v>
+        <v>14.70321989127454</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.328642714284484</v>
+        <v>0.657907471799552</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.033252415517794</v>
+        <v>0.1940779122433235</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8045</v>
+        <v>8092</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>499.0813996738649</v>
+        <v>506.2331153808416</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>54.7</v>
+        <v>12.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.96274235633214</v>
+        <v>50.33847867004186</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.1772627369831</v>
+        <v>15.39221296088219</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4701276801042962</v>
+        <v>1.328642714284484</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2365124876216324</v>
+        <v>0.0332524154096353</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8367</v>
+        <v>8045</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>497.9840804412044</v>
+        <v>499.0813996738651</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>41.6</v>
+        <v>54.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.98935951084854</v>
+        <v>52.96274278218532</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.31772053093062</v>
+        <v>23.17726264892726</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7507174748594028</v>
+        <v>0.4701276801042962</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1127191634574138</v>
+        <v>0.2365124856988621</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8182</v>
+        <v>8367</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>491.1710001944109</v>
+        <v>497.9840804412044</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>40.9</v>
+        <v>41.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.80746527738344</v>
+        <v>61.98935945991586</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.24974944477152</v>
+        <v>15.31772047322008</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6050046484498443</v>
+        <v>0.7507174748594028</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.148134812560415</v>
+        <v>0.1127191635054785</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8109</v>
+        <v>8182</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>490.3547156277512</v>
+        <v>491.1710001944109</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>134</v>
+        <v>40.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.15619948273217</v>
+        <v>47.80746529659933</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.53979905973742</v>
+        <v>26.2497494681898</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6966858094218231</v>
+        <v>0.6050046484498443</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.2938768419039048</v>
+        <v>0.148134812560415</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8466</v>
+        <v>8109</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>484.0961964598022</v>
+        <v>490.354715627751</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15.1</v>
+        <v>134</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.18431000183927</v>
+        <v>50.15619942168075</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.68166236365013</v>
+        <v>25.53979892203228</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1044384423329265</v>
+        <v>0.6966858094218231</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0475142988273811</v>
+        <v>-0.2938768413270332</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8044</v>
+        <v>8466</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>480.3590397207177</v>
+        <v>484.0961964598022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>24.35</v>
+        <v>15.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.96078101764368</v>
+        <v>48.18431002689659</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.86383257176385</v>
+        <v>23.68166234886271</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8530220267614552</v>
+        <v>0.1044384423329265</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1140736280280247</v>
+        <v>0.0475142987913289</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8463</v>
+        <v>8044</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>475.091663621972</v>
+        <v>480.3590397207176</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>21.2</v>
+        <v>24.35</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.28982963979887</v>
+        <v>51.96078121601373</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25.92820695166806</v>
+        <v>17.86383270475373</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4763150049988324</v>
+        <v>0.8530220267614552</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0152223408877706</v>
+        <v>0.1140736279559185</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8443</v>
+        <v>8463</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>472.6294915453217</v>
+        <v>475.0916636219719</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11.15</v>
+        <v>21.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.69589492510588</v>
+        <v>49.28982985342291</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>51.9441058781426</v>
+        <v>25.92820695952522</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2253584794126979</v>
+        <v>0.4763150049988324</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.4004028861588741</v>
+        <v>0.015222340827683</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8940</v>
+        <v>8443</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>469.1943337779754</v>
+        <v>472.6294915453217</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>15.15</v>
+        <v>11.15</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.76266827526828</v>
+        <v>51.69589492323538</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.84139502252704</v>
+        <v>51.94410593096711</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5846929827848519</v>
+        <v>0.2253584794126979</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0503074209769196</v>
+        <v>-0.4004028861468572</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8064</v>
+        <v>8940</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>463.7474974314114</v>
+        <v>469.1943337779755</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>121</v>
+        <v>15.15</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.6515058657864</v>
+        <v>52.76266840309591</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.15037488770502</v>
+        <v>13.84139507375777</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.592296099388596</v>
+        <v>0.5846929827848519</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-2.355441221459497</v>
+        <v>0.0503074209408681</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8097</v>
+        <v>8064</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>457.7159413065388</v>
+        <v>463.7474974314114</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>48.6</v>
+        <v>121</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.75365133394945</v>
+        <v>43.6515058982099</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.15598544127269</v>
+        <v>21.15037503217743</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4688054946869823</v>
+        <v>0.592296099388596</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>2</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.07010849328536629</v>
+        <v>-2.355441221807997</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8049</v>
+        <v>8097</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>442.0841682405832</v>
+        <v>457.7159413065388</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.35</v>
+        <v>48.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.76931560070487</v>
+        <v>45.75365207263426</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.68698315744137</v>
+        <v>16.15598540846658</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.131013432574954</v>
+        <v>0.4688054946869823</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0167792258985953</v>
+        <v>0.07010849309309369</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8162</v>
+        <v>8049</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>434.0077428320859</v>
+        <v>442.0841682405832</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>62.7</v>
+        <v>24.35</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.73933214483747</v>
+        <v>41.76931576027983</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.89357392977931</v>
+        <v>13.68698321683001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6741843706886207</v>
+        <v>1.131013432574954</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.07603442812829959</v>
+        <v>0.016779225838509</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8048</v>
+        <v>8162</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>426.7978243132777</v>
+        <v>434.007742832086</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>50.9</v>
+        <v>62.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.63551998698281</v>
+        <v>47.73933215566829</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.47885201637728</v>
+        <v>23.89357395541358</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7463844239687545</v>
+        <v>0.6741843706886207</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2832491567312456</v>
+        <v>-0.076034428140316</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>9912</v>
+        <v>8048</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>426.623705948912</v>
+        <v>426.7978243132777</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13</v>
+        <v>50.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.82731469277787</v>
+        <v>49.63551998196967</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>35.32872109194172</v>
+        <v>13.47885223284886</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6655562435140532</v>
+        <v>0.7463844239687545</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.4791565450021027</v>
+        <v>0.2832491566230891</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8088</v>
+        <v>9912</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>421.4580241840866</v>
+        <v>426.623705948912</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43.6</v>
+        <v>13</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.51610734221426</v>
+        <v>51.82731470398641</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.17280890262589</v>
+        <v>35.3287210684647</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.98906825806431</v>
+        <v>0.6655562435140532</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2792560815124039</v>
+        <v>-0.4791565450501734</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8477</v>
+        <v>8088</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>420.4358470608719</v>
+        <v>421.4580241840866</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.85</v>
+        <v>43.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.41768405298905</v>
+        <v>48.51610747161138</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30.86433405816672</v>
+        <v>15.17280903757645</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.95602839945103</v>
+        <v>1.98906825806431</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0461130877366876</v>
+        <v>0.279256081536438</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8227</v>
+        <v>8477</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>420.0543325402336</v>
+        <v>420.4358470608719</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>292</v>
+        <v>13.85</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.18220405386551</v>
+        <v>37.41768404163923</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>43.39883107281738</v>
+        <v>30.86433411959664</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.108583215215279</v>
+        <v>1.95602839945103</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-7.531684262606532</v>
+        <v>-0.0461130877366876</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8341</v>
+        <v>8227</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>417.9601690736355</v>
+        <v>420.0543325402336</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>292</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.69254944729347</v>
+        <v>51.18220410557163</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.69460089430604</v>
+        <v>43.39883109000623</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.126713967371728</v>
+        <v>1.108583215215279</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0217179530937298</v>
+        <v>-7.531684263808238</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8454</v>
+        <v>8341</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>417.7951221605604</v>
+        <v>417.9601690736355</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>242</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.33068949510532</v>
+        <v>42.69254988181969</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.48137471899821</v>
+        <v>12.69460100181331</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6286068010749192</v>
+        <v>1.126713967371728</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.8141724585933479</v>
+        <v>0.0217179529254726</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8147</v>
+        <v>8454</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>417.3813983406134</v>
+        <v>417.7951221605604</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.59392862271236</v>
+        <v>48.33068930457354</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>29.89859145223783</v>
+        <v>11.48137481993253</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.9958754387737044</v>
+        <v>0.6286068010749192</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.7294539880244644</v>
+        <v>0.8141724585933479</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8080</v>
+        <v>8147</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>416.8384932578459</v>
+        <v>417.3813983406137</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>27.75</v>
+        <v>137</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.00818707489504</v>
+        <v>49.59392876418908</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.62734790878424</v>
+        <v>29.89859158269091</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4.083849325784596</v>
+        <v>0.9958754387737044</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3233300661566892</v>
+        <v>-0.729453989466549</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8071</v>
+        <v>8080</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>415.5777824041429</v>
+        <v>416.8384932578459</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>20.85</v>
+        <v>27.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>34.33727214684798</v>
+        <v>51.00818647858291</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.00262160229938</v>
+        <v>28.62734337984391</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.599836756700089</v>
+        <v>4.083849325784596</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.002438532768959</v>
+        <v>0.3233300731026888</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8404</v>
+        <v>8071</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>412.664878362621</v>
+        <v>415.5777824041432</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.5</v>
+        <v>20.85</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.66417100319732</v>
+        <v>34.33727237914233</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>41.09654583304042</v>
+        <v>11.00262163813732</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6304419256923839</v>
+        <v>1.599836756700089</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1267592905047244</v>
+        <v>0.0024385325887009</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8478</v>
+        <v>8404</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>412.2278975311148</v>
+        <v>412.6648783626209</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>140</v>
+        <v>13.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.01350655090806</v>
+        <v>39.66417105373327</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.887695932966388</v>
+        <v>41.09654585295949</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.438622837088018</v>
+        <v>0.6304419256923839</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1333452458412427</v>
+        <v>0.1267592905287595</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8102</v>
+        <v>8478</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>410.5862043111889</v>
+        <v>412.2278975311148</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.51403070374899</v>
+        <v>45.01350674381489</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4.672774289958388</v>
+        <v>7.887696000303691</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2475125905908365</v>
+        <v>1.438622837088018</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.191577604133095</v>
+        <v>0.1333452462017577</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8121</v>
+        <v>8102</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>409.9884605899286</v>
+        <v>410.5862043111889</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.6778168343926</v>
+        <v>50.51403073049835</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.8927503859264</v>
+        <v>4.672774261337965</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6274004678193441</v>
+        <v>0.2475125905908365</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.3208101434349646</v>
+        <v>1.19157760353223</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8054</v>
+        <v>8121</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>407.8261152449755</v>
+        <v>409.9884605899283</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>32</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>32.20666372033199</v>
+        <v>54.67781689844541</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.35582037958972</v>
+        <v>33.89275045883612</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.409962073434924</v>
+        <v>0.6274004678193441</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.9862765636333868</v>
+        <v>0.3208101434469794</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8072</v>
+        <v>8054</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>403.5057116885299</v>
+        <v>407.8261152449757</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>26.55</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.02185826834283</v>
+        <v>32.20666382937877</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>34.14817595273016</v>
+        <v>20.35582041516897</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2961901448299546</v>
+        <v>1.409962073434924</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1179878190629815</v>
+        <v>-0.9862765642342552</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8039</v>
+        <v>8072</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>399.75650988352</v>
+        <v>403.5057116885298</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>275.5</v>
+        <v>26.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.34578865080152</v>
+        <v>44.02185766287674</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.63247833099539</v>
+        <v>34.14817619807797</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.175983615449735</v>
+        <v>0.2961901448299546</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0377477387860816</v>
+        <v>-0.1179878186784307</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8074</v>
+        <v>8039</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>395.8237108165307</v>
+        <v>399.75650988352</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>54</v>
+        <v>275.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.28105517961603</v>
+        <v>47.34578868024552</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.61574113918156</v>
+        <v>19.63247845287703</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7109108807843214</v>
+        <v>1.175983615449735</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5202696851714386</v>
+        <v>0.0377477375242714</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8110</v>
+        <v>8074</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>390.4916913771934</v>
+        <v>395.8237108165307</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>47.15</v>
+        <v>54</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.39801524356968</v>
+        <v>50.28105538759137</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.56676875940701</v>
+        <v>22.61574129905681</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4880418814816649</v>
+        <v>0.7109108807843214</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.057092262313986</v>
+        <v>0.5202696842941666</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8087</v>
+        <v>8110</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>390.1322597125599</v>
+        <v>390.4916913771934</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>22.95</v>
+        <v>47.15</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.42615966378439</v>
+        <v>49.39801527987289</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4.855729496974499</v>
+        <v>27.5667688832987</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2303846989784829</v>
+        <v>0.4880418814816649</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0158985169012193</v>
+        <v>-0.0570922623860916</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8411</v>
+        <v>8087</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>386.1523409468449</v>
+        <v>390.1322597125599</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11.65</v>
+        <v>22.95</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>29.36851971580555</v>
+        <v>48.42615968899588</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>38.75667943552595</v>
+        <v>4.855729472190188</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.668023812169151</v>
+        <v>0.2303846989784829</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0280488980501757</v>
+        <v>0.0158985167449933</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8488</v>
+        <v>8411</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>374.3607786760758</v>
+        <v>386.1523409468449</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>9.68</v>
+        <v>11.65</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.15535743151524</v>
+        <v>29.36851967376376</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>34.48884692669761</v>
+        <v>38.75667937988662</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6577330593039801</v>
+        <v>0.668023812169151</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>1</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1945178880649372</v>
+        <v>-0.0280488980261411</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8091</v>
+        <v>8488</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>371.3870835672213</v>
+        <v>374.3607786760758</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>216</v>
+        <v>9.68</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.88703768762375</v>
+        <v>51.15535742482455</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.09590172075587</v>
+        <v>34.48884690767725</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7902547400729121</v>
+        <v>0.6577330593039801</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4701557521946289</v>
+        <v>-0.1945178880529208</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8155</v>
+        <v>8091</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>362.1105815981019</v>
+        <v>371.3870835672213</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.60515324533821</v>
+        <v>44.88703771421783</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.88750392644364</v>
+        <v>19.09590185725991</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.197857188812564</v>
+        <v>0.7902547400729121</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.011917868430277</v>
+        <v>0.4701557518341024</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8481</v>
+        <v>8155</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>358.6506878441401</v>
+        <v>362.1105815981019</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>40.9</v>
+        <v>312</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.86378384306874</v>
+        <v>42.60515331395197</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.02375565144227</v>
+        <v>11.88750418047916</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3776731455088436</v>
+        <v>1.197857188812564</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0252322987332071</v>
+        <v>-1.011917870953911</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9930</v>
+        <v>8481</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>358.4405354529804</v>
+        <v>358.6506878441401</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>60.3</v>
+        <v>40.9</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.2968879086229</v>
+        <v>51.86378373697511</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>35.31944957474037</v>
+        <v>13.02375581031464</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.352039933543321</v>
+        <v>0.3776731455088436</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,48 +5022,48 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0019284262108474</v>
+        <v>-0.0252322987332071</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8183</v>
+        <v>9930</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>355.8634049635203</v>
+        <v>358.4405354529804</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>28.2</v>
+        <v>60.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G87" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.90268828233761</v>
+        <v>46.2968879768038</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.14537626240933</v>
+        <v>35.31944959959962</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>1.352039933543321</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,84 +5075,84 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.06862061036835659</v>
+        <v>-0.0019284262348849</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8299</v>
+        <v>8183</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>353.7836197785974</v>
+        <v>355.8634049635201</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1965</v>
+        <v>28.2</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G88" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.36194817573481</v>
+        <v>44.90268854970988</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.26022909910575</v>
+        <v>19.14537644421087</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.581019204635296</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-14.58053846362156</v>
+        <v>0.0686206099749555</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9955</v>
+        <v>8299</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>351.5031403676087</v>
+        <v>353.7836197785969</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>23.2</v>
+        <v>1965</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.57691162730475</v>
+        <v>39.3619481553682</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.13481058503978</v>
+        <v>12.26022915617037</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.048105477240496</v>
+        <v>1.581019204635296</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.09697278781031329</v>
+        <v>-14.58053846169884</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8462</v>
+        <v>9955</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>350.9901591227321</v>
+        <v>351.5031403676091</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>153</v>
+        <v>23.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>31.9835682129902</v>
+        <v>44.57691179461707</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>35.20787865424027</v>
+        <v>13.13481064183193</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.133355488403366</v>
+        <v>1.048105477240496</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.2193676846964622</v>
+        <v>0.09697278772619081</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8059</v>
+        <v>8462</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>344.5289445089656</v>
+        <v>350.9901591227321</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.3</v>
+        <v>153</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>55.08291394207935</v>
+        <v>31.98356836061193</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28.20577791776878</v>
+        <v>35.20787867672411</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.147626833108771</v>
+        <v>1.133355488403366</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0595405259652768</v>
+        <v>-0.2193676855377004</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8422</v>
+        <v>8059</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>342.7423655901117</v>
+        <v>344.5289445089656</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>25.1</v>
+        <v>17.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.08325591159233</v>
+        <v>55.08291416041473</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8.035857255868791</v>
+        <v>28.20577777617685</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.16876383700792</v>
+        <v>1.147626833108771</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0235037996660986</v>
+        <v>0.0595405255533669</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8176</v>
+        <v>8422</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>326.2641156970246</v>
+        <v>342.7423655901117</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>37.81485110444993</v>
+        <v>38.08325675876797</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.6844633103819</v>
+        <v>8.035857270457468</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.881835609872993</v>
+        <v>1.16876383700792</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0093929317127935</v>
+        <v>-0.0235038006958774</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8096</v>
+        <v>8176</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>321.2202968368016</v>
+        <v>326.2641156970249</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>86.2</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.44480169935014</v>
+        <v>37.81485132619674</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>30.20814143421929</v>
+        <v>24.6844634831359</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9675866206916182</v>
+        <v>0.881835609872993</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>1</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>1.22266071281463</v>
+        <v>-0.009392931736828499</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>9136</v>
+        <v>8096</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>311.8499966602412</v>
+        <v>321.2202968368014</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>9.1</v>
+        <v>86.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>30.59548379061196</v>
+        <v>35.44480182371201</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.7619714394183</v>
+        <v>30.2081414463217</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.762360986335536</v>
+        <v>0.9675866206916182</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0543277248156734</v>
+        <v>1.222660712766547</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8487</v>
+        <v>9136</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>303.0973313162179</v>
+        <v>311.8499966602412</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.7</v>
+        <v>9.1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.53388261362306</v>
+        <v>30.59548379960344</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.5784046416942</v>
+        <v>15.76197143502662</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6789934605529848</v>
+        <v>1.762360986335536</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0033098802899163</v>
+        <v>0.0543277248060602</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8047</v>
+        <v>8487</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>298.4561719228437</v>
+        <v>303.0973313162179</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>44.7</v>
+        <v>69.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.35713026107957</v>
+        <v>39.53388277531522</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.03157255737648</v>
+        <v>11.578404645236</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1853891455380892</v>
+        <v>0.6789934605529848</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1874010335484264</v>
+        <v>0.0033098803379847</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8390</v>
+        <v>8047</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>297.0391489663335</v>
+        <v>298.4561719228422</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>90.5</v>
+        <v>44.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.11981151838409</v>
+        <v>50.35713025616821</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.17675610081874</v>
+        <v>8.031572475178388</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9213391511567472</v>
+        <v>0.1853891455380892</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.3607547205778858</v>
+        <v>0.1874010336926361</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8410</v>
+        <v>8390</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>294.1948785436049</v>
+        <v>297.0391489663338</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.4</v>
+        <v>90.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>19.70438388930785</v>
+        <v>43.11981157339301</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>51.37954657429415</v>
+        <v>18.17675608353649</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4981551424858037</v>
+        <v>0.9213391511567472</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1103600248006789</v>
+        <v>0.360754720601923</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8271</v>
+        <v>8410</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>289.0313016763089</v>
+        <v>294.1948785436049</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>189.5</v>
+        <v>26.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>30.24022910368051</v>
+        <v>19.70438438757164</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.51486563078957</v>
+        <v>51.37954657429416</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.30882357219435</v>
+        <v>0.4981551424858037</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.3347681255985506</v>
+        <v>-0.1103600249689211</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8429</v>
+        <v>8271</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>279.8100992769312</v>
+        <v>289.0313016763092</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>5.87</v>
+        <v>189.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.74096922864334</v>
+        <v>30.2402291545357</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.498065817753826</v>
+        <v>15.51486574739902</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.450082500867959</v>
+        <v>1.30882357219435</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0042432005066999</v>
+        <v>-0.3347681258388792</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8472</v>
+        <v>8429</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>274.5595255955872</v>
+        <v>279.8100992769312</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>65</v>
+        <v>5.87</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.05409314896453</v>
+        <v>38.74096946602256</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>29.40915317042983</v>
+        <v>8.498065829477222</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1559525595587189</v>
+        <v>1.450082500867959</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.123125709829162</v>
+        <v>0.0042432005091039</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8473</v>
+        <v>8472</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>255.8806533739514</v>
+        <v>274.5595255955872</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>38.35</v>
+        <v>65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>36.32871524136107</v>
+        <v>36.05409370050354</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.10623233693389</v>
+        <v>29.40915315401149</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.430500143887447</v>
+        <v>0.1559525595587189</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1805255697580003</v>
+        <v>-1.123125710574235</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8499</v>
+        <v>8473</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>252.237693940719</v>
+        <v>255.8806533739516</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>249</v>
+        <v>38.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.70254294520219</v>
+        <v>36.32871558241078</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.086487223143171</v>
+        <v>20.10623241093465</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8595313980767602</v>
+        <v>1.430500143887447</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1.374648899693555</v>
+        <v>0.1805255695416866</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8076</v>
+        <v>8499</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>248.0864904304136</v>
+        <v>252.237693940719</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>20.65</v>
+        <v>249</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>31.17843709703889</v>
+        <v>49.70254304190932</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>23.81520029189018</v>
+        <v>8.086487233038433</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.065723434876873</v>
+        <v>0.8595313980767602</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0058361954304617</v>
+        <v>1.374648892603383</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8104</v>
+        <v>8076</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>240.7658646172638</v>
+        <v>248.0864904304149</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>30.3</v>
+        <v>20.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.36114026922343</v>
+        <v>31.17843734258065</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.39474486088224</v>
+        <v>23.815200326984</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7687263618215029</v>
+        <v>2.065723434876873</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0049333097252634</v>
+        <v>-0.0058361954544963</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8222</v>
+        <v>8104</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>239.5498375692734</v>
+        <v>240.7658646172656</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>34.75</v>
+        <v>30.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.63849218641425</v>
+        <v>42.36114093998137</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.542709234580817</v>
+        <v>15.39474492153688</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8519553534434279</v>
+        <v>0.7687263618215029</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0739689753930871</v>
+        <v>-0.0049333100497297</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8210</v>
+        <v>8222</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>237.1345697045734</v>
+        <v>239.5498375692734</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>838</v>
+        <v>34.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.05150576090762</v>
+        <v>37.63849268747006</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.05025085962669</v>
+        <v>8.542709404288454</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.178009500900723</v>
+        <v>0.8519553534434279</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>3.12045066749494</v>
+        <v>0.07396897481625379</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8291</v>
+        <v>8210</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>231.5122754614854</v>
+        <v>237.1345697045735</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>26.3</v>
+        <v>838</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>33.1160642181117</v>
+        <v>36.05150581632962</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6.486133163742372</v>
+        <v>19.05025089237972</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.690358091797009</v>
+        <v>1.178009500900723</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0207107568558151</v>
+        <v>3.120450665331749</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8101</v>
+        <v>8291</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>223.4063728883034</v>
+        <v>231.5122754614855</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10.3</v>
+        <v>26.3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.4393734032486</v>
+        <v>33.11628077916369</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.61878363032869</v>
+        <v>6.486872573548351</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.523759108177119</v>
+        <v>1.690358091797009</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.09673986226463779</v>
+        <v>-0.0207150683174994</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8261</v>
+        <v>8101</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>212.9031315251782</v>
+        <v>223.4063728883035</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>166.5</v>
+        <v>10.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.15843431932097</v>
+        <v>42.43937343073624</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.10326232419319</v>
+        <v>18.61878364879263</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.740956200408603</v>
+        <v>0.523759108177119</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1761276097498357</v>
+        <v>-0.0967398622886706</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8067</v>
+        <v>8261</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>204.1230777788625</v>
+        <v>212.9031315251778</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>11.1</v>
+        <v>166.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>40.23667903930817</v>
+        <v>41.15843434418872</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.81180951154334</v>
+        <v>16.10326243372463</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2289456839795172</v>
+        <v>0.740956200408603</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0480300682356397</v>
+        <v>-0.1761276101343692</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8374</v>
+        <v>8067</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>178.1902288150679</v>
+        <v>204.1230777788625</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>73.2</v>
+        <v>11.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.06909914604564</v>
+        <v>40.23667915547947</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.79700600218403</v>
+        <v>17.81180951425274</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7502452782860533</v>
+        <v>0.2289456839795172</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1813170656352483</v>
+        <v>-0.0480300683197605</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8163</v>
+        <v>8374</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>138.7046939086239</v>
+        <v>178.1902288150677</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>29.1</v>
+        <v>73.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.53705990646471</v>
+        <v>35.06909937111016</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.22193541742979</v>
+        <v>12.79700601392615</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.495206618226682</v>
+        <v>0.7502452782860533</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0219154179346588</v>
+        <v>-0.1813170667167873</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,52 +6516,105 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>8163</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>達方</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>138.7046939086239</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>36.53706012382534</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>13.22193550649422</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.495206618226682</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.021915418126934</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
         <v>8105</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>凌巨</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>117.1113189944137</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>14.55</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>42.1546937115566</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>17.73013487026998</v>
-      </c>
-      <c r="J115" s="2" t="n">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>42.15469389780372</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>17.73013495282875</v>
+      </c>
+      <c r="J116" s="2" t="n">
         <v>0.816125958973918</v>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>0.0178248300152956</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0178248299390163</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
